--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>13053.22</v>
+        <v>12922.94</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6575.1</v>
+        <v>6566.73</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10473.38</v>
+        <v>10654.16</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12202.38</v>
+        <v>12259.21</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13471.12</v>
+        <v>13296.99</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6523.45</v>
+        <v>6548.16</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10174.56</v>
+        <v>10111.48</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9943.58</v>
+        <v>9988.74</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2380-2488-CM25</t>
+          <t>2859-221-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12922.94</v>
+        <v>13631.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>820-44-CM25</t>
+          <t>2380-2488-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6566.73</v>
+        <v>12922.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>820-49-CM25</t>
+          <t>820-44-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10654.16</v>
+        <v>6566.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1346283-253-CM25</t>
+          <t>820-49-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12259.21</v>
+        <v>10654.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1208093-106-CM25</t>
+          <t>1346283-253-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13296.99</v>
+        <v>12259.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2175-173-CM26</t>
+          <t>1208093-106-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6548.16</v>
+        <v>13296.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1171166-150-CM26</t>
+          <t>2175-173-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10111.48</v>
+        <v>6548.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1638-296-CM26</t>
+          <t>1171166-150-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.250.500-k</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,6 +996,67 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>10111.48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1638-296-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.250.500-k</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>9988.74</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2859-221-CM25</t>
+          <t>1392207-17-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,22 +529,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>65.195.573-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ATACAMA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>13631.01</v>
+        <v>24039.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2380-2488-CM25</t>
+          <t>2859-221-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>12922.94</v>
+        <v>13631.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>820-44-CM25</t>
+          <t>751-165-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6566.73</v>
+        <v>15078.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>820-49-CM25</t>
+          <t>2175-129-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,28 +752,28 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10654.16</v>
+        <v>8265.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1346283-253-CM25</t>
+          <t>1180885-6-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12259.21</v>
+        <v>37258.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1208093-106-CM25</t>
+          <t>1346283-161-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13296.99</v>
+        <v>7636.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2175-173-CM26</t>
+          <t>2380-1875-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6548.16</v>
+        <v>16460.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1171166-150-CM26</t>
+          <t>820-39-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10111.48</v>
+        <v>8413.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1638-296-CM26</t>
+          <t>1467796-6-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.250.500-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,6 +1057,555 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
+        <v>13972.81</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1467796-5-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>13348.96</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2380-2488-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>12922.94</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>820-44-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>6566.73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>820-49-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>10654.16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1346283-253-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>12259.21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1208093-106-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>13296.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2175-173-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>6548.16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1171166-150-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>10111.48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1638-296-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.250.500-k</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
         <v>9988.74</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -819,7 +835,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1346283-161-CM25</t>
+          <t>1079486-82-SE25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +850,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +860,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,28 +875,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>76.559.762-5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7636.88</v>
+        <v>6346.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2380-1875-CM25</t>
+          <t>1346283-161-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +910,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,28 +940,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16460.12</v>
+        <v>7636.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>820-39-CM25</t>
+          <t>2380-1875-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +975,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +990,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,28 +1005,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8413.5</v>
+        <v>16460.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1467796-6-CM25</t>
+          <t>820-39-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1045,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1055,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1050,20 +1078,24 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13972.81</v>
+        <v>8413.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1467796-5-CM25</t>
+          <t>1467796-6-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1111,35 +1143,39 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>13348.96</v>
+        <v>13972.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2380-2488-CM25</t>
+          <t>1467796-5-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1185,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1200,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>12922.94</v>
+        <v>13348.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>820-44-CM25</t>
+          <t>2380-2488-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1240,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1250,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,28 +1265,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6566.73</v>
+        <v>12922.94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>820-49-CM25</t>
+          <t>820-44-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1305,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,28 +1330,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10654.16</v>
+        <v>6566.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1346283-253-CM25</t>
+          <t>820-49-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1370,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,28 +1395,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12259.21</v>
+        <v>10654.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1208093-106-CM25</t>
+          <t>1346283-253-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1430,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1445,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,28 +1460,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13296.99</v>
+        <v>12259.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2175-173-CM26</t>
+          <t>1208093-106-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1495,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1525,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6548.16</v>
+        <v>13296.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1171166-150-CM26</t>
+          <t>2175-173-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1560,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1590,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,67 +1605,136 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>10111.48</v>
+        <v>6548.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>1171166-150-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>10111.48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>1638-296-CM26</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>jun-2026</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>69.250.500-k</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>MELMAN SPA</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>9988.74</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1738,6 +1738,132 @@
         <v>9988.74</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2859-1212-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>12661.84</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2322-801-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>26770.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1741,7 +1741,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2859-1212-CM26</t>
+          <t>2322-777-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1781,86 +1781,151 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12661.84</v>
+        <v>6765.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>2859-1212-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>12661.84</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>2322-801-CM26</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>69.030.500-3</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>MELMAN SPA</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>26770.61</v>
       </c>
     </row>
